--- a/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:31</t>
+          <t>2026-10-06 01:23:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:32</t>
+          <t>2026-10-06 01:23:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:34</t>
+          <t>2026-10-06 01:23:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:35</t>
+          <t>2026-10-06 01:23:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:35</t>
+          <t>2026-10-06 01:23:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:35</t>
+          <t>2026-10-06 01:23:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:35</t>
+          <t>2026-10-06 01:23:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:35</t>
+          <t>2026-10-06 01:23:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:35</t>
+          <t>2026-10-06 01:23:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2575</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.53%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1325</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+9.93%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>5700</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+4.34%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>5165</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+4.22%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3585</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5.96%7205</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+5.96%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7205</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0%626</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>626</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+6.37%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2005</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+3.95%5520</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+3.95%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5520</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+2.4%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1495</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.6%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>2075</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.57%152.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.57%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>152.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+9.88%1780</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+9.88%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1780</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.17%2485</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.17%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2485</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:12</t>
+          <t>2026-10-06 02:26:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.12%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2150</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:18</t>
+          <t>2026-10-06 02:26:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:29</t>
+          <t>2026-10-06 02:26:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:31</t>
+          <t>2026-10-06 02:27:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,27 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2585</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.83%11,464,000</t>
+          <t>10.00%11,464,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.83%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,40 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+5.18%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5995</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.87%20,100,000</t>
+          <t>9.41%4,650,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.87%</t>
+          <t>9.41%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>20100000</v>
+        <v>4650000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,40 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.13%1310</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1310</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.82%4,650,000</t>
+          <t>8.53%19,300,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.82%</t>
+          <t>8.53%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4650000</v>
+        <v>19300000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,27 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.74%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4920</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.75%5,086,000</t>
+          <t>8.44%5,086,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>8.44%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,27 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.79%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>3685</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.24%6,062,000</t>
+          <t>7.54%6,062,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.24%</t>
+          <t>7.54%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,27 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.73%7080</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.73%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>7080</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.00%2,502,000</t>
+          <t>5.98%2,502,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>5.98%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -882,40 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.24%2050</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.24%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2050</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.16%24,757,000</t>
+          <t>5.11%7,389,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.16%</t>
+          <t>5.11%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>24757000</v>
+        <v>7389000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -945,40 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.16%625</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>625</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.93%7,389,000</t>
+          <t>4.96%23,519,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>4.96%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7389000</v>
+        <v>23519000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,27 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.72%5670</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.72%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5670</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.59%2,499,000</t>
+          <t>4.78%2,499,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.78%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,27 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.67%1505</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.67%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1505</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.45%8,937,000</t>
+          <t>4.54%8,937,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>4.54%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.2%2050</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.2%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>2050</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,35 +1180,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.28%147.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.28%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>147.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.30%84,618,000</t>
+          <t>3.96%79,618,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>84618000</v>
+        <v>79618000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,35 +1241,33 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.4%1755</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1755</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.65%6,151,000</t>
+          <t>3.83%6,467,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>6151000</v>
+        <v>6467000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1323,40 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+6.51%2290</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+6.51%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2290</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.21%3,876,848</t>
+          <t>3.33%4,315,561</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>3876848</v>
+        <v>4315561</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:33</t>
+          <t>2026-10-06 19:14:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1386,40 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-6.44%2325</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-6.44%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2325</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.09%4,315,561</t>
+          <t>2.67%3,405,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>2.67%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>4315561</v>
+        <v>3405848</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,27 +1424,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+4.07%742</t>
+          <t>+0.27%744</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.29%9,276,000</t>
+          <t>2.33%9,276,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1482,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1512,40 +1482,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.51%294</t>
+          <t>-2.62%8375</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-2.62%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.27%12,938,450</t>
+          <t>1.47%520,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>12938450</v>
+        <v>520000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1575,40 +1545,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+8.86%8600</t>
+          <t>+3.7%1260</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+8.86%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.11%388,000</t>
+          <t>1.35%3,164,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>388000</v>
+        <v>3164000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1638,40 +1608,40 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+3.61%19520</t>
+          <t>+1.36%298</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>298</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.10%168,900</t>
+          <t>1.30%12,938,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>168900</v>
+        <v>12938450</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1701,40 +1671,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+9.95%1215</t>
+          <t>-2.74%18985</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+9.95%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.00%2,483,000</t>
+          <t>1.01%157,900</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2483000</v>
+        <v>157900</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1769,35 +1739,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+6.06%2450</t>
+          <t>-1.43%2415</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+6.06%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.98%1,204,000</t>
+          <t>0.56%692,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1204000</v>
+        <v>692000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1827,40 +1797,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+2.67%576</t>
+          <t>+0.31%1600</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+2.67%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.67%3,483,000</t>
+          <t>0.26%476,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3483000</v>
+        <v>476000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1895,17 +1865,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.14%3105</t>
+          <t>-1.61%3055</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1923,7 +1893,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1953,40 +1923,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+5.63%1595</t>
+          <t>-1.21%6130</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+5.63%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.25%476,000</t>
+          <t>0.19%93,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>476000</v>
+        <v>93000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,40 +1986,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8210勤誠</t>
+          <t>6271同欣電</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+5.83%890</t>
+          <t>0%238.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+5.83%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>238.5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.20%683,000</t>
+          <t>0.18%2,185,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>683000</v>
+        <v>2185000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2079,40 +2049,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>8210勤誠</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+2.22%6205</t>
+          <t>-0.56%885</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>885</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.19%93,000</t>
+          <t>0.14%478,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>93000</v>
+        <v>478000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2142,36 +2112,36 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6271同欣電</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.71%238.5</t>
+          <t>+1.05%86.8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>238.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.17%2,185,000</t>
+          <t>0.11%3,921,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2185000</v>
+        <v>3921000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2205,36 +2175,36 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6191精成科</t>
+          <t>3376新日興</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.42%85.9</t>
+          <t>0%171.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>171.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.11%3,921,000</t>
+          <t>0.10%1,740,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3921000</v>
+        <v>1740000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:45</t>
+          <t>2026-10-06 19:14:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2268,40 +2238,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3376新日興</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.44%171.5</t>
+          <t>+3.02%1535</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>171.5</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.10%1,740,000</t>
+          <t>0.06%121,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1740000</v>
+        <v>121000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2331,38 +2301,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.43%241.5</t>
+          <t>+1.41%252</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>241.5</v>
+        <v>252</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.06%698,000</t>
+          <t>0.04%501,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>698000</v>
+        <v>501000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2392,38 +2362,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+9.96%1490</t>
+          <t>+0.26%18.95</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1490</v>
+        <v>18.95</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.06%121,000</t>
+          <t>0.03%5,163,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>121000</v>
+        <v>5163000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2453,34 +2423,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+9.96%248.5</t>
+          <t>+1.86%246</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>248.5</v>
+        <v>246</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.04%501,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>501000</v>
+        <v>1000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2519,29 +2489,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.38%220</t>
+          <t>+6.36%234</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>+6.36%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.03%448,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>448000</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2575,38 +2545,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2002中鋼</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.53%18.9</t>
+          <t>-3.33%551</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>18.9</v>
+        <v>551</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.03%5,163,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>5163000</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2636,21 +2606,21 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+9.83%570</t>
+          <t>+5.82%4180</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+9.83%</t>
+          <t>+5.82%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>570</v>
+        <v>4180</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2697,21 +2667,21 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2439美律</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+3.67%3950</t>
+          <t>-0.13%75.2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+3.67%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3950</v>
+        <v>75.2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2758,21 +2728,21 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2439美律</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.53%75.3</t>
+          <t>+1.27%1195</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>75.3</v>
+        <v>1195</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2819,21 +2789,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0%1180</t>
+          <t>+1.86%6855</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1180</v>
+        <v>6855</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2880,21 +2850,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+7%6730</t>
+          <t>-0.35%574</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6730</v>
+        <v>574</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2946,16 +2916,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.3%331</t>
+          <t>+0.76%333.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>331</v>
+        <v>333.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3007,16 +2977,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+2.22%598</t>
+          <t>-5.02%568</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>598</v>
+        <v>568</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3068,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.76%530</t>
+          <t>-0.94%525</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3129,16 +3099,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.11%97.7</t>
+          <t>+2.35%100</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>+2.35%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:26:56</t>
+          <t>2026-10-06 19:14:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3190,16 +3160,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+6.16%2325</t>
+          <t>+1.08%2350</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:07</t>
+          <t>2026-10-06 19:14:25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3251,16 +3221,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.84%1180</t>
+          <t>+2.12%1205</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1180</v>
+        <v>1205</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:07</t>
+          <t>2026-10-06 19:14:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3312,16 +3282,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0%574</t>
+          <t>-1.92%563</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:07</t>
+          <t>2026-10-06 19:14:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3373,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.36%124</t>
+          <t>+2.82%127.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>124</v>
+        <v>127.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:07</t>
+          <t>2026-10-06 19:14:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3434,16 +3404,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.2%254</t>
+          <t>+0.79%256</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:07</t>
+          <t>2026-10-06 19:14:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3495,16 +3465,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.6%184</t>
+          <t>+3.8%191</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>+3.8%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:07</t>
+          <t>2026-10-06 19:14:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3556,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+3.44%180.5</t>
+          <t>-2.49%176</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+3.44%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>180.5</v>
+        <v>176</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:19</t>
+          <t>2026-10-06 23:18:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:22</t>
+          <t>2026-10-06 23:18:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:24</t>
+          <t>2026-10-06 23:18:46</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:25</t>
+          <t>2026-10-06 23:18:48</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:25</t>
+          <t>2026-10-06 23:18:48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:25</t>
+          <t>2026-10-06 23:18:48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:25</t>
+          <t>2026-10-06 23:18:48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:25</t>
+          <t>2026-10-06 23:18:48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 19:14:25</t>
+          <t>2026-10-06 23:18:48</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.39%2585</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.39%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2585</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+5.18%5995</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+5.18%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5995</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.13%1310</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1310</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-4.74%4920</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-4.74%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>4920</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.79%3685</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.79%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3685</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.73%7080</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.73%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7080</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.24%2050</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.24%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2050</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.16%625</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.16%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>625</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.72%5670</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+2.72%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>5670</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.67%1505</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.67%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1505</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.2%2050</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.2%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>2050</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.28%147.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.28%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>147.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.4%1755</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.4%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1755</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+6.51%2290</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+6.51%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2290</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:42</t>
+          <t>2026-10-06 23:26:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.44%2325</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.44%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2325</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:45</t>
+          <t>2026-10-06 23:26:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:46</t>
+          <t>2026-10-06 23:27:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:48</t>
+          <t>2026-10-06 23:27:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:48</t>
+          <t>2026-10-06 23:27:18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:48</t>
+          <t>2026-10-06 23:27:18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:48</t>
+          <t>2026-10-06 23:27:18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:48</t>
+          <t>2026-10-06 23:27:18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:48</t>
+          <t>2026-10-06 23:27:18</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:44</t>
+          <t>2026-10-06 23:57:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:26:56</t>
+          <t>2026-10-06 23:57:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:07</t>
+          <t>2026-10-06 23:57:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:18</t>
+          <t>2026-10-06 23:57:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
